--- a/04_DESIGN_TABLES/DesignTable_1502_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1502_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF2"/>
+  <dimension ref="A1:BF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,6 +896,1378 @@
       <c r="BF2" t="inlineStr">
         <is>
           <t>1502-02-02-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1502-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1502-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF (female) x 3/8-18 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>3/8-18 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-06-06-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 0d65652c456fb904...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>1502-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1502-12-08-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1502-12-08-FG</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF (female) x 1/2-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1/2-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-12-08-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 05173adef898c6c2...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>1502-12-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1502-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1502-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF (female) x 3/4-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>3/4-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-12-12-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 541b6ec909ac5ef7...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>1502-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1502-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.63957</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.6750699999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1502-16-16-FG</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF (female) x 1-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N3@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "L LGTH" = "1.620" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); M1@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "M LGTH" = "1.730" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel stem tip (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); W3@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "M1 LGTH" = "2.080" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); CHEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); C1HEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - body hex (forged flats) (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); D@BORE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "A2 DRILL" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - swivel stem bore (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); TAPDRILL@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-12-16) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPSM swivel thread = 1.315 (ASME B1.20.1 pipe OD, ms51500.py NPTF[16]; the value every 1405 / 1502 row carries for its NPSM end) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes; = OMi WebsitePartsInfo2026 Items Side 1 / Side 2 Thread and Brennan TFA p.21 A1 NPTF / A2 NPSM "1-11-1/2" | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>1502-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1502-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9048</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08253</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8141</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.6405</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.80957</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.84707</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.08203</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1502-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-20-20-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 9ec6af161e958a81...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>1502-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1502-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.22687</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.9392</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.92957</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.96657</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.73822</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.73822</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.47694</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1502-24-24-FG</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-24-24 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-24-24-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 2de88b184d18f1f4...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>1502-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1502-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.4055</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.4055</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.0215</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.2766</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.51554</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.0985</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.16457</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.20357</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.4055</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.4055</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.81097</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.81097</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.62243</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1502-32-32-FG</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 2-11 1/2 NPTF (female) x 2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-32-32 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-32-32-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 faca6632b6a167d4...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>1502-32-32-FG</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_1502_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1502_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF9"/>
+  <dimension ref="A1:BF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,161 +706,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1502-02-02-FG</t>
+          <t>1502-08-08-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.75</v>
+        <v>1.23</v>
       </c>
       <c r="C2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.28</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.2496</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.32332</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.1984</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.1572</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.1984</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.2275</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.3066</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.1725</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.15</v>
-      </c>
       <c r="W2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.33</v>
+        <v>0.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.75</v>
+        <v>1.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.89</v>
+        <v>1.52</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.33</v>
+        <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.46</v>
+        <v>0.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.03704</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.165</v>
+        <v>0.35</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.19463</v>
+        <v>0.40714</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.75</v>
+        <v>1.23</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.364</v>
+        <v>0.759</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1736</v>
+        <v>0.388</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.03704</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.182</v>
+        <v>0.3795</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.21163</v>
+        <v>0.43664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.89</v>
+        <v>1.52</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.062</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.49</v>
+        <v>0.97</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.062</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.28</v>
+        <v>0.531</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.28</v>
+        <v>0.531</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.16116</v>
+        <v>0.30607</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.16116</v>
+        <v>0.30607</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.32282</v>
+        <v>0.61265</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1502-02-02-FG</t>
+          <t>1502-08-08-FG</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1/8-27 NPTF (female) x 1/8-27 NPSM (female swivel)</t>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1/2-14 NPTF (female) x 1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1/8-27 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -885,178 +885,178 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>Air-Way s114 only (double-pass 16 rows) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the round collar of the female pipe leg (0.26, measured on the -04 / -06 / -08 / -16 forgings, applied to -02) and the NPSM swivel end (Brennan 1404 STEPs); the sizes of the part are Air-Way's | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_1502-08-08-FG.stp, every value equal to the catalog within 0.005); end details from the end library: N3@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "L LGTH" = "1.23" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face; own STEP: port face 1.23 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); M1@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "M LGTH" = "1.24" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel stem tip; own STEP: stem bore runs to 1.24 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); W3@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "M1 LGTH" = "1.52" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face; own STEP: nut face 1.52 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); CHEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "C HEX" = "1.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; own STEP: nut A/F 1.000 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py), npsm.py); C1HEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - body hex (forged flats); own STEP: body A/F 1.062, corner radius 0.6131 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); D@BORE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "A2 DRILL" = "0.460" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - swivel stem bore; own STEP: bore 0.460 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); TAPDRILL@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718 behind a 0.75 tapered port - the end library value is kept as on every sibling); THDMAJ_A@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -08 NPSM swivel thread = 0.84 (ASME B1.20.1 pipe OD, ms51500.py NPTF[8]; the value every 1405 / 1502 row carries for its NPSM end) [Q-TRANSFER-ENDLIB yes 2026-10-08] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - CONFIRMED on the Brennan 1502-08-08-FG elbow forging: its hex arm ends 0.48 behind the stem tip, at 0.76 from the crossing); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2026-10-02 cross-check, Brennan TFA catalog p21 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf, table TFA-p021-t01 in tools/_out/brennan_catalog_20261001/catalog_verified.json, verified; re-read from the PDF text layer 2026-10-02) 1502-02-02-FG: DIFFERS on N3 0.75 vs L 0.660; M1 0.74 vs M 0.800; W3 0.89 vs M1 0.940; D 0.13 vs A2 DRILL 0.110 (Air-Way vs Brennan); agrees on CHEX 0.56, C1HEX 0.56 (within rounding) - built to Air-Way (OMi gives no dimensions for this part; no size is taken from Brennan (user ruling 2026-10-08: Brennan for shape only)) - flag for OMi</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 1502-8-8 (plain): N3 1.25 W3 1.33 M1 1.00 CHEX 1.00 C1HEX 1.00 TAPDRILL 0.70 D 0.45 (differs from the forged part on N3 / W3 / M1 / C1HEX) | Brennan 1502-08-08-FG STEP (2026-10-02, tools/measure/fgelbow.py + npsm.py --leg 1,1): the row values are this STEP (forged part built from its own Brennan STEP): port face 1.230 (N3), nut face 1.520 (W3), stem tip 1.240 (M1), body hex 1.062 (corner radius 0.6131 = the 30deg puck radius), nut hex 1.000, NPSM bore 0.460, tap drill 0.718, round collar 0.26 x dia 1.062 at the port, swivel body face 0.76; the NPSM swivel end equals NPSM_MEAS[8] (Brennan 1404-08-08) on every value; Brennan TFA catalog p21 prints the same L/M/M1/C/Y/A2 DRILL. NOT modelled: the thread-zone minor cone and the port-mouth 45deg chamfer, the ball end of the tap drill past the crossing, the nut 30deg face chamfer and 45deg rear hex chamfer, the nut rear undercut and the nut/body joint, 0.01 fillets, the 0.002 deep marking on the hex flats</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1502-02-02-FG</t>
+          <t>1502-08-08-FG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1502-06-06-FG</t>
+          <t>1502-02-02-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.02</v>
+        <v>0.75</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4375</v>
+        <v>0.28</v>
       </c>
       <c r="D3" t="n">
-        <v>1.27</v>
+        <v>0.89</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4375</v>
+        <v>0.28</v>
       </c>
       <c r="F3" t="n">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2465</v>
+        <v>0.129</v>
       </c>
       <c r="H3" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4056</v>
+        <v>0.2496</v>
       </c>
       <c r="J3" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4375</v>
+        <v>0.28</v>
       </c>
       <c r="L3" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.50518</v>
+        <v>0.32332</v>
       </c>
       <c r="N3" t="n">
-        <v>0.331</v>
+        <v>0.1984</v>
       </c>
       <c r="O3" t="n">
-        <v>0.306</v>
+        <v>0.182</v>
       </c>
       <c r="P3" t="n">
-        <v>0.265</v>
+        <v>0.1572</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.331</v>
+        <v>0.1984</v>
       </c>
       <c r="R3" t="n">
-        <v>0.36</v>
+        <v>0.2275</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4707</v>
+        <v>0.3066</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2935</v>
+        <v>0.1725</v>
       </c>
       <c r="U3" t="n">
-        <v>0.211</v>
+        <v>0.117</v>
       </c>
       <c r="V3" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="W3" t="n">
-        <v>0.875</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.02</v>
+        <v>0.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>0.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.05556</v>
+        <v>0.03704</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.32944</v>
+        <v>0.19463</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>0.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.612</v>
+        <v>0.364</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.29</v>
+        <v>0.1736</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.05556</v>
+        <v>0.03704</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.306</v>
+        <v>0.182</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.35044</v>
+        <v>0.21163</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.27</v>
+        <v>0.89</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.875</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.76</v>
+        <v>0.49</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.875</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.4375</v>
+        <v>0.28</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.4375</v>
+        <v>0.28</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.25209</v>
+        <v>0.16116</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.25209</v>
+        <v>0.16116</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.50468</v>
+        <v>0.32282</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1502-06-06-FG</t>
+          <t>1502-02-02-FG</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF (female) x 3/8-18 NPSM (female swivel)</t>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1/8-27 NPTF (female) x 1/8-27 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3/8-18 NPSM (female swivel)</t>
+          <t>1/8-27 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1081,178 +1081,178 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-06-06-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 0d65652c456fb904...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s114 only (double-pass 16 rows) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the round collar of the female pipe leg (0.26, measured on the -04 / -06 / -08 / -16 forgings, applied to -02) and the NPSM swivel end (Brennan 1404 STEPs); the sizes of the part are Air-Way's | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+          <t>2026-10-02 cross-check, Brennan TFA catalog p21 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf, table TFA-p021-t01 in tools/_out/brennan_catalog_20261001/catalog_verified.json, verified; re-read from the PDF text layer 2026-10-02) 1502-02-02-FG: DIFFERS on N3 0.75 vs L 0.660; M1 0.74 vs M 0.800; W3 0.89 vs M1 0.940; D 0.13 vs A2 DRILL 0.110 (Air-Way vs Brennan); agrees on CHEX 0.56, C1HEX 0.56 (within rounding) - built to Air-Way (OMi gives no dimensions for this part; no size is taken from Brennan (user ruling 2026-10-08: Brennan for shape only)) - flag for OMi</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1502-06-06-FG</t>
+          <t>1502-02-02-FG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1502-12-08-FG</t>
+          <t>1502-04-04-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.36</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.656</v>
+        <v>0.345</v>
       </c>
       <c r="D4" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>0.656</v>
+        <v>0.345</v>
       </c>
       <c r="F4" t="n">
-        <v>0.76</v>
+        <v>0.58</v>
       </c>
       <c r="G4" t="n">
-        <v>0.304</v>
+        <v>0.1825</v>
       </c>
       <c r="H4" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="I4" t="n">
-        <v>0.455</v>
+        <v>0.3146</v>
       </c>
       <c r="J4" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0.345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.57735</v>
+        <v>0.39837</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4115</v>
+        <v>0.263</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3795</v>
+        <v>0.2405</v>
       </c>
       <c r="P4" t="n">
-        <v>0.356</v>
+        <v>0.265</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4115</v>
+        <v>0.263</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4425</v>
+        <v>0.29</v>
       </c>
       <c r="S4" t="n">
-        <v>0.595</v>
+        <v>0.4459</v>
       </c>
       <c r="T4" t="n">
-        <v>0.37</v>
+        <v>0.225</v>
       </c>
       <c r="U4" t="n">
-        <v>0.281</v>
+        <v>0.1485</v>
       </c>
       <c r="V4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="X4" t="n">
         <v>0.28</v>
       </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.4</v>
-      </c>
       <c r="Y4" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.36</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.455</v>
+        <v>0.215</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.51214</v>
+        <v>0.25944</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.759</v>
+        <v>0.481</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.388</v>
+        <v>0.2875</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.3795</v>
+        <v>0.2405</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.43664</v>
+        <v>0.28494</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.312</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.312</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.656</v>
+        <v>0.345</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.656</v>
+        <v>0.345</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.37824</v>
+        <v>0.19869</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.37824</v>
+        <v>0.19869</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.75698</v>
+        <v>0.39787</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1502-12-08-FG</t>
+          <t>1502-04-04-FG</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF (female) x 1/2-14 NPSM (female swivel)</t>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1/4-18 NPTF (female) x 1/4-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1/2-14 NPSM (female swivel)</t>
+          <t>1/4-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1277,178 +1277,178 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-12-08-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 05173adef898c6c2...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-CELL 2026-10-21: M1@DRIVE, W3@HEX] Air-Way s114 only (double-pass 16 rows) | M1@DRIVE 0.99 / W3@HEX 1.18: Brennan TFA catalog p.21 TFA-p021-t01 row 1502-04-04-FG "M LGTH" 0.990 / "M1 LGTH" 1.180 - Air-Way M1 0.78 / W3 0.97 cannot be built (swivel body face inside the hex corner), user rule 2026-10-20 Q1 "use brennans"; the other cells stay Air-Way s114 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+          <t>2026-10-02 cross-check, Brennan TFA catalog p21 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf, table TFA-p021-t01 in tools/_out/brennan_catalog_20261001/catalog_verified.json, verified; re-read from the PDF text layer 2026-10-02) 1502-04-04-FG: DIFFERS on N3 0.94 vs L 0.880; M1 0.78 vs M 0.990; W3 0.97 vs M1 1.180; C1HEX 0.69 vs Y FLATS 0.750 (Air-Way vs Brennan); agrees on CHEX 0.69, D 0.22 (within rounding) - modelled to Air-Way (OMi gives no dimensions for this part; Brennan-only values wait for Q-BRENNAN-ONLY) - NOT BUILT: gen_tee BLOCKS this row (review 2026-10-02): with Air-Way M1 0.78 the swivel body face (0.39 = M1 - the Brennan 1404-04 body-to-tip 0.39, ASSUMED for the elbow) lies inside the hex corner radius (0.398 = C1HEX 0.69 / sqrt3), so the pipe-leg hex arm corner would stand 0.008 beyond it outside the swivel neck; Brennan faces that off at the body face (6500-05-05-FG STEP) and the 90 deg elbow has no facing cut. Brennan's own -04-04-FG (M 0.99, Y FLATS 0.750) would put the body face at about 0.60 with the same body-to-tip, clear of its corner radius 0.433 - flag for OMi | 2026-10-21 batch 19 C (staged): M1@DRIVE 0.78 -&gt; 0.99 and W3@HEX 0.97 -&gt; 1.18 (Brennan TFA p21) by the Q1 rule (Air-Way value not buildable -&gt; Brennan); the row now generates. Alternative: all four differing cells Brennan (N3 0.88, C1HEX 0.75 too) - also generates (C_ownstep/checks/test_1502-04-04-FG.txt). Tell the user these cells</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1502-12-08-FG</t>
+          <t>1502-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1502-12-12-FG</t>
+          <t>1502-06-06-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="C5" t="n">
-        <v>0.656</v>
+        <v>0.4375</v>
       </c>
       <c r="D5" t="n">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="E5" t="n">
-        <v>0.656</v>
+        <v>0.4375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="G5" t="n">
-        <v>0.389</v>
+        <v>0.2465</v>
       </c>
       <c r="H5" t="n">
-        <v>0.745</v>
+        <v>0.58</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5694</v>
+        <v>0.4056</v>
       </c>
       <c r="J5" t="n">
-        <v>0.135</v>
+        <v>0.125</v>
       </c>
       <c r="K5" t="n">
-        <v>0.625</v>
+        <v>0.4375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.50518</v>
       </c>
       <c r="N5" t="n">
-        <v>0.517</v>
+        <v>0.331</v>
       </c>
       <c r="O5" t="n">
-        <v>0.485</v>
+        <v>0.306</v>
       </c>
       <c r="P5" t="n">
-        <v>0.361</v>
+        <v>0.265</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.517</v>
+        <v>0.331</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5625</v>
+        <v>0.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6189</v>
+        <v>0.4707</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4635</v>
+        <v>0.2935</v>
       </c>
       <c r="U5" t="n">
-        <v>0.375</v>
+        <v>0.211</v>
       </c>
       <c r="V5" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>0.875</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.455</v>
+        <v>0.285</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.51214</v>
+        <v>0.32944</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.97</v>
+        <v>0.612</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.393</v>
+        <v>0.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.485</v>
+        <v>0.306</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.54214</v>
+        <v>0.35044</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.312</v>
+        <v>0.875</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.312</v>
+        <v>0.875</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.02</v>
+        <v>0.65</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.656</v>
+        <v>0.4375</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.656</v>
+        <v>0.4375</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.37824</v>
+        <v>0.25209</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.37824</v>
+        <v>0.25209</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.75698</v>
+        <v>0.50468</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1502-12-12-FG</t>
+          <t>1502-06-06-FG</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF (female) x 3/4-14 NPSM (female swivel)</t>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF (female) x 3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3/4-14 NPSM (female swivel)</t>
+          <t>3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -1473,178 +1473,178 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-12-12-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 541b6ec909ac5ef7...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-06-06-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 0d65652c456fb904...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1502-12-12-FG</t>
+          <t>1502-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1502-16-16-FG</t>
+          <t>1502-12-08-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8125</v>
+        <v>0.656</v>
       </c>
       <c r="D6" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8125</v>
+        <v>0.656</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="G6" t="n">
-        <v>0.525</v>
+        <v>0.304</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7098</v>
+        <v>0.455</v>
       </c>
       <c r="J6" t="n">
-        <v>0.175</v>
+        <v>0.14</v>
       </c>
       <c r="K6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.86603</v>
+        <v>0.57735</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6465</v>
+        <v>0.4115</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6055</v>
+        <v>0.3795</v>
       </c>
       <c r="P6" t="n">
-        <v>0.428</v>
+        <v>0.356</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6465</v>
+        <v>0.4115</v>
       </c>
       <c r="R6" t="n">
-        <v>0.67</v>
+        <v>0.4425</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7447</v>
+        <v>0.595</v>
       </c>
       <c r="T6" t="n">
-        <v>0.59</v>
+        <v>0.37</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4845</v>
+        <v>0.281</v>
       </c>
       <c r="V6" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.63957</v>
+        <v>0.51214</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.211</v>
+        <v>0.759</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.469</v>
+        <v>0.388</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.6055</v>
+        <v>0.3795</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.6750699999999999</v>
+        <v>0.43664</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.625</v>
+        <v>1.312</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.625</v>
+        <v>1.312</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.8125</v>
+        <v>0.656</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.8125</v>
+        <v>0.656</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4686</v>
+        <v>0.37824</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.4686</v>
+        <v>0.37824</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.93769</v>
+        <v>0.75698</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1502-16-16-FG</t>
+          <t>1502-12-08-FG</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF (female) x 1-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF (female) x 1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -1669,178 +1669,178 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N3@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "L LGTH" = "1.620" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); M1@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "M LGTH" = "1.730" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel stem tip (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); W3@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "M1 LGTH" = "2.080" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); CHEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); C1HEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - body hex (forged flats) (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); D@BORE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "A2 DRILL" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - swivel stem bore (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); TAPDRILL@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-12-16) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPSM swivel thread = 1.315 (ASME B1.20.1 pipe OD, ms51500.py NPTF[16]; the value every 1405 / 1502 row carries for its NPSM end) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes; = OMi WebsitePartsInfo2026 Items Side 1 / Side 2 Thread and Brennan TFA p.21 A1 NPTF / A2 NPSM "1-11-1/2" | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-12-08-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 05173adef898c6c2...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1502-16-16-FG</t>
+          <t>1502-12-08-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1502-20-20-FG</t>
+          <t>1502-12-12-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9375</v>
+        <v>0.656</v>
       </c>
       <c r="D7" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9375</v>
+        <v>0.656</v>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.695</v>
+        <v>0.389</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.745</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9048</v>
+        <v>0.5694</v>
       </c>
       <c r="J7" t="n">
-        <v>0.195</v>
+        <v>0.135</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9375</v>
+        <v>0.625</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08253</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.819</v>
+        <v>0.517</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7775</v>
+        <v>0.485</v>
       </c>
       <c r="P7" t="n">
-        <v>0.497</v>
+        <v>0.361</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.819</v>
+        <v>0.517</v>
       </c>
       <c r="R7" t="n">
-        <v>0.85</v>
+        <v>0.5625</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8141</v>
+        <v>0.6189</v>
       </c>
       <c r="T7" t="n">
-        <v>0.768</v>
+        <v>0.4635</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6405</v>
+        <v>0.375</v>
       </c>
       <c r="V7" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.875</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.01</v>
+        <v>0.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.74</v>
+        <v>0.455</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.80957</v>
+        <v>0.51214</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.555</v>
+        <v>0.97</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.5385</v>
+        <v>0.393</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.7775</v>
+        <v>0.485</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.84707</v>
+        <v>0.54214</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.875</v>
+        <v>1.312</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.875</v>
+        <v>1.312</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.9375</v>
+        <v>0.656</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.9375</v>
+        <v>0.656</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.54077</v>
+        <v>0.37824</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.54077</v>
+        <v>0.37824</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.08203</v>
+        <v>0.75698</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1502-20-20-FG</t>
+          <t>1502-12-12-FG</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF (female) x 3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -1865,178 +1865,178 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-20-20-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 9ec6af161e958a81...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-12-12-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 541b6ec909ac5ef7...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1502-20-20-FG</t>
+          <t>1502-12-12-FG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1502-24-24-FG</t>
+          <t>1502-16-16-FG</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D8" t="n">
         <v>2.08</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.2795</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.83</v>
-      </c>
       <c r="E8" t="n">
-        <v>1.2795</v>
+        <v>0.8125</v>
       </c>
       <c r="F8" t="n">
-        <v>1.165</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8075</v>
+        <v>0.525</v>
       </c>
       <c r="H8" t="n">
-        <v>1.125</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.027</v>
+        <v>0.7098</v>
       </c>
       <c r="J8" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1.22687</v>
+        <v>0.86603</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9385</v>
+        <v>0.6465</v>
       </c>
       <c r="O8" t="n">
-        <v>0.897</v>
+        <v>0.6055</v>
       </c>
       <c r="P8" t="n">
-        <v>0.503</v>
+        <v>0.428</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9385</v>
+        <v>0.6465</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9675</v>
+        <v>0.67</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9392</v>
+        <v>0.7447</v>
       </c>
       <c r="T8" t="n">
-        <v>0.879</v>
+        <v>0.59</v>
       </c>
       <c r="U8" t="n">
-        <v>0.75</v>
+        <v>0.4845</v>
       </c>
       <c r="V8" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="W8" t="n">
-        <v>2.125</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2.08</v>
       </c>
-      <c r="AA8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
         <v>0.08696</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.92957</v>
+        <v>0.63957</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.794</v>
+        <v>1.211</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.5445</v>
+        <v>0.469</v>
       </c>
       <c r="AK8" t="n">
         <v>0.08696</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.897</v>
+        <v>0.6055</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.96657</v>
+        <v>0.6750699999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.83</v>
+        <v>2.08</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.559</v>
+        <v>1.625</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.559</v>
+        <v>1.625</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.665</v>
+        <v>1.14</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.2795</v>
+        <v>0.8125</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.2795</v>
+        <v>0.8125</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.73822</v>
+        <v>0.4686</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.73822</v>
+        <v>0.4686</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.47694</v>
+        <v>0.93769</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1502-24-24-FG</t>
+          <t>1502-16-16-FG</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF (female) x 1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPSM (female swivel)</t>
+          <t>1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -2061,211 +2061,603 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-24-24 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-24-24-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 2de88b184d18f1f4...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N3@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "L LGTH" = "1.620" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); M1@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "M LGTH" = "1.730" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel stem tip (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); W3@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "M1 LGTH" = "2.080" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); CHEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); C1HEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - body hex (forged flats) (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); D@BORE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "A2 DRILL" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - swivel stem bore (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); TAPDRILL@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-12-16) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPSM swivel thread = 1.315 (ASME B1.20.1 pipe OD, ms51500.py NPTF[16]; the value every 1405 / 1502 row carries for its NPSM end) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes; = OMi WebsitePartsInfo2026 Items Side 1 / Side 2 Thread and Brennan TFA p.21 A1 NPTF / A2 NPSM "1-11-1/2" | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1502-24-24-FG</t>
+          <t>1502-16-16-FG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1502-32-32-FG</t>
+          <t>1502-20-20-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4055</v>
+        <v>0.9375</v>
       </c>
       <c r="D9" t="n">
-        <v>2.99</v>
+        <v>2.25</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4055</v>
+        <v>0.9375</v>
       </c>
       <c r="F9" t="n">
-        <v>1.165</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0215</v>
+        <v>0.695</v>
       </c>
       <c r="H9" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2766</v>
+        <v>0.9048</v>
       </c>
       <c r="J9" t="n">
         <v>0.195</v>
       </c>
       <c r="K9" t="n">
-        <v>1.31</v>
+        <v>0.9375</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>1.51554</v>
+        <v>1.08253</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1755</v>
+        <v>0.819</v>
       </c>
       <c r="O9" t="n">
-        <v>1.134</v>
+        <v>0.7775</v>
       </c>
       <c r="P9" t="n">
-        <v>0.502</v>
+        <v>0.497</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.1755</v>
+        <v>0.819</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2125</v>
+        <v>0.85</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9385</v>
+        <v>0.8141</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0985</v>
+        <v>0.768</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0.6405</v>
       </c>
       <c r="V9" t="n">
         <v>0.42</v>
       </c>
       <c r="W9" t="n">
-        <v>2.625</v>
+        <v>1.875</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.99</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
         <v>0.08696</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.095</v>
+        <v>0.74</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.16457</v>
+        <v>0.80957</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.268</v>
+        <v>1.555</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5435</v>
+        <v>0.5385</v>
       </c>
       <c r="AK9" t="n">
         <v>0.08696</v>
       </c>
       <c r="AL9" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.84707</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.08203</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1502-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-20-20-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 9ec6af161e958a81...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>1502-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1502-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.22687</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.9392</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.92957</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.96657</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.73822</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.73822</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.47694</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>1502-24-24-FG</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-24-24 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-24-24-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 2de88b184d18f1f4...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>1502-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1502-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.4055</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.4055</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.0215</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2766</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.51554</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.134</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="P11" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.0985</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.16457</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="AM11" t="n">
         <v>1.20357</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AN11" t="n">
         <v>2.99</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AO11" t="n">
         <v>2.811</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AP11" t="n">
         <v>2.13</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ11" t="n">
         <v>2.811</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR11" t="n">
         <v>1.825</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS11" t="n">
         <v>1.4055</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AT11" t="n">
         <v>1.4055</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AU11" t="n">
         <v>0.81097</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AV11" t="n">
         <v>0.81097</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AW11" t="n">
         <v>1.62243</v>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>1502-32-32-FG</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>90 deg Female Pipe x Female NPSM Swivel Elbow, 2-11 1/2 NPTF (female) x 2-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>1502</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>2-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-32-32 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-32-32-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 faca6632b6a167d4...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP; CONFIRMED on the pilot Brennan 1502-08-08-FG STEP, tools/measure/fgelbow.py: hex arms with flats normal to Z, corner = 30deg double cone about Z of the hex corner radius, within 0.0001): one hex arm along each leg, A/F = the row body hex C1HEX (Air-Way; no JIC leg), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = the row CHEX (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging of this size: measured on an elbow forging only at 1502-08-08-FG (hex arm ends 0.48 behind the stem tip = the 1404-08 straight); no 1502 forging of this size measured); NUT FACE AT THE ROW W3 AND STEM TIP AT THE ROW M1 (pipe-leg axis to the nut face / to the stem tip; Air-Way; shape check: the Brennan 1502-08-08-FG part has W3 - M1 = 0.28); where W3 - M1 differs from the Brennan 1404 nut-face-to-stem-tip the row is followed (user decision 2026-09-24) and the row carries a warning; NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF leg: tap drill = the row TAPDRILL (Air-Way) from the port face to the axis crossing, tapered helical thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - the Brennan 1502-08-08-FG and 5504-08-08-FG STEPs show this tap drill running on below the thread to the crossing (Brennan 1502: it ends in a ball 0.23 past the crossing, at the far wall of the NPSM bore; modelled with a flat end at the crossing: ASSUMPTION, the NPSM bore opens into it); the thread-zone minor cone (1.79deg, -08: dia 0.791 -&gt; 0.747 over 0.75 deep) and the 45deg port-mouth chamfer are NOT modelled (the helical thread represents the thread zone; its length is MS51503 P1 max, 0.90 at -08, vs the Brennan thread zone 0.75); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP)</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>1502-32-32-FG</t>
         </is>
